--- a/docs/analyses/swanzey-financial-review/Models/Swanzey Financial Model.xlsx
+++ b/docs/analyses/swanzey-financial-review/Models/Swanzey Financial Model.xlsx
@@ -13,6 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Elections" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pains Register" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tax Rates" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Capital Projects" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Capital 10-Year Plan" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,8 +23,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="$#,##0;[Red]-$#,##0"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -84,7 +87,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -101,6 +104,9 @@
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -995,6 +1001,9 @@
         <f>B11-C11</f>
         <v/>
       </c>
+      <c r="F11" s="5" t="n">
+        <v>0.677</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1033,6 +1042,9 @@
         <f>B13-C13</f>
         <v/>
       </c>
+      <c r="F13" s="5" t="n">
+        <v>0.662</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1071,6 +1083,9 @@
         <f>B15-C15</f>
         <v/>
       </c>
+      <c r="F15" s="5" t="n">
+        <v>0.581</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1089,6 +1104,9 @@
       <c r="E16" s="4">
         <f>B16-C16</f>
         <v/>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0.741</v>
       </c>
     </row>
     <row r="17">
@@ -2807,4 +2825,541 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Capital Backlog — Project Inventory</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>The fix for Finding 4 (3/5 wall). Costs are planning estimates; confirm with engineering.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Project</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Total Cost</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Local Tax Share</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Local %</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Primary funding path</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Public Works Facility</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="D5" s="5">
+        <f>C5/B5</f>
+        <v/>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>RSA 35 capital reserve (pay-go)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Christian Hill Road Bridge</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>200000</v>
+      </c>
+      <c r="D6" s="5">
+        <f>C6/B6</f>
+        <v/>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>RSA 234 state bridge aid 80% + reserve</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Lower Winchester Street</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>750000</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>480000</v>
+      </c>
+      <c r="D7" s="5">
+        <f>C7/B7</f>
+        <v/>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Highway block grant + roads reserve</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>West Swanzey Water System</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>2075000</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="5">
+        <f>C8/B8</f>
+        <v/>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>NHDES DWSRF (water rates) + grants + forgiveness</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Town Hall ADA Stairwell</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>250000</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>125000</v>
+      </c>
+      <c r="D9" s="5">
+        <f>C9/B9</f>
+        <v/>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>CDBG/accessibility grant + facilities reserve</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B10" s="12">
+        <f>SUM(B5:B9)</f>
+        <v/>
+      </c>
+      <c r="C10" s="12">
+        <f>SUM(C5:C9)</f>
+        <v/>
+      </c>
+      <c r="D10" s="13">
+        <f>C10/B10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Non-property-tax share</t>
+        </is>
+      </c>
+      <c r="B12" s="5">
+        <f>1-C10/B10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>New bonds required</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>$0 — all majority-vote reserves</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Capital Reserve Deposit Schedule &amp; Tax Impact</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Modeled. Majority-vote RSA 35 deposits; net-new impact peaks then drops below today.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>PW Facility</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Bridge</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Roads</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Hwy Equip</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Fire App.</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Total deposits</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>Net-new $/$300k home</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>150000</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>100000</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>90000</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>70000</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>40000</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I5" s="12">
+        <f>SUM(B5:H5)</f>
+        <v/>
+      </c>
+      <c r="J5" s="14" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2028</v>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>250000</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>100000</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>90000</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>70000</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>40000</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I6" s="12">
+        <f>SUM(B6:H6)</f>
+        <v/>
+      </c>
+      <c r="J6" s="14" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2029</v>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>250000</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>100000</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>90000</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>70000</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>40000</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I7" s="12">
+        <f>SUM(B7:H7)</f>
+        <v/>
+      </c>
+      <c r="J7" s="14" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2030</v>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>300000</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>25000</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>100000</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>90000</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>70000</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>40000</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I8" s="12">
+        <f>SUM(B8:H8)</f>
+        <v/>
+      </c>
+      <c r="J8" s="14" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2031</v>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>250000</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>25000</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>100000</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>90000</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>70000</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>40000</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I9" s="12">
+        <f>SUM(B9:H9)</f>
+        <v/>
+      </c>
+      <c r="J9" s="14" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2032</v>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>25000</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>100000</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>90000</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>70000</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>40000</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I10" s="12">
+        <f>SUM(B10:H10)</f>
+        <v/>
+      </c>
+      <c r="J10" s="14" t="n">
+        <v>-18</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2033</v>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>25000</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>100000</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>90000</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>70000</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>40000</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I11" s="12">
+        <f>SUM(B11:H11)</f>
+        <v/>
+      </c>
+      <c r="J11" s="14" t="n">
+        <v>-18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/analyses/swanzey-financial-review/Models/Swanzey Financial Model.xlsx
+++ b/docs/analyses/swanzey-financial-review/Models/Swanzey Financial Model.xlsx
@@ -812,14 +812,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Swanzey Operating &amp; Default Budget — 2015–2025</t>
+          <t>Swanzey Operating &amp; Default Budget — by Town-Meeting Year (2012–2026)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: Town of Swanzey Annual Reports (actual, voted figures). Provenance: real.</t>
+          <t>Operating = warrant (proposed) figure, keyed to meeting year; deliberative amendments minor (e.g., 2020 adopted $6,330,000). Source: Town of Swanzey Annual Reports; 2026 news.</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="B5" s="4" t="n">
         <v>5747885</v>
@@ -870,12 +870,12 @@
         <v/>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.801040312093628</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="B6" s="4" t="n">
         <v>5824380</v>
@@ -892,12 +892,12 @@
         <v/>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.801</v>
+        <v>0.7689594356261023</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="B7" s="4" t="n">
         <v>5888782</v>
@@ -914,12 +914,12 @@
         <v/>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.769</v>
+        <v>0.8075040783034259</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="B8" s="4" t="n">
         <v>6012393</v>
@@ -936,12 +936,12 @@
         <v/>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.7656427758816836</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="B9" s="4" t="n">
         <v>6262426</v>
@@ -958,12 +958,12 @@
         <v/>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.766</v>
+        <v>0.6829765545361876</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="B10" s="4" t="n">
         <v>6210799</v>
@@ -980,12 +980,12 @@
         <v/>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.676923076923077</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="B11" s="4" t="n">
         <v>6210799</v>
@@ -1001,13 +1001,10 @@
         <f>B11-C11</f>
         <v/>
       </c>
-      <c r="F11" s="5" t="n">
-        <v>0.677</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="B12" s="4" t="n">
         <v>6452435</v>
@@ -1023,10 +1020,13 @@
         <f>B12-C12</f>
         <v/>
       </c>
+      <c r="F12" s="5" t="n">
+        <v>0.6622950819672131</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="B13" s="4" t="n">
         <v>6303000</v>
@@ -1042,13 +1042,10 @@
         <f>B13-C13</f>
         <v/>
       </c>
-      <c r="F13" s="5" t="n">
-        <v>0.662</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="B14" s="4" t="n">
         <v>6716500</v>
@@ -1064,16 +1061,19 @@
         <f>B14-C14</f>
         <v/>
       </c>
+      <c r="F14" s="5" t="n">
+        <v>0.5806745670009116</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="B15" s="4" t="n">
         <v>6902500</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>6680348</v>
+        <v>6864706</v>
       </c>
       <c r="D15" s="5">
         <f>(B15-B14)/B14</f>
@@ -1084,18 +1084,18 @@
         <v/>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.581</v>
+        <v>0.7413622902270484</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="B16" s="4" t="n">
         <v>7425000</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>6864706</v>
+        <v>7468834</v>
       </c>
       <c r="D16" s="5">
         <f>(B16-B15)/B15</f>
@@ -1106,18 +1106,18 @@
         <v/>
       </c>
       <c r="F16" s="5" t="n">
-        <v>0.741</v>
+        <v>0.6217948717948718</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B17" s="4" t="n">
         <v>7961500</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>7468834</v>
+        <v>7935699</v>
       </c>
       <c r="D17" s="5">
         <f>(B17-B16)/B16</f>
@@ -1128,12 +1128,12 @@
         <v/>
       </c>
       <c r="F17" s="5" t="n">
-        <v>0.622</v>
+        <v>0.5820189274447949</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B18" s="4" t="n">
         <v>8370000</v>
@@ -1150,12 +1150,12 @@
         <v/>
       </c>
       <c r="F18" s="5" t="n">
-        <v>0.582</v>
+        <v>0.5730659025787965</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B19" s="4" t="n">
         <v>8939036</v>
@@ -1171,14 +1171,11 @@
         <f>B19-C19</f>
         <v/>
       </c>
-      <c r="F19" s="5" t="n">
-        <v>0.573</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Growth 2011→2025</t>
+          <t>Growth 2012→2026</t>
         </is>
       </c>
       <c r="B21" s="5">
@@ -1189,7 +1186,7 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Recent CAGR (2021→2025)</t>
+          <t>Recent CAGR (2022→2026)</t>
         </is>
       </c>
       <c r="B22" s="5">
@@ -1200,7 +1197,7 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>2025 default gap %</t>
+          <t>2026 default gap %</t>
         </is>
       </c>
       <c r="B23" s="5">
@@ -1232,14 +1229,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Operating Budget Forecast — 2026–2030</t>
+          <t>Operating Budget Forecast — 2027–2031</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Modeled. Base 6.0% off the real 2025 voted budget; low 4.5% / high 7.5% (recent CAGR ≈ 6.7%).</t>
+          <t>Modeled. Base 6.0% off the 2026 adopted budget ($8,939,036); low 4.5% / high 7.5% (recent CAGR ≈ 6.7%).</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1280,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025 base</t>
+          <t>2026 base</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
@@ -1314,7 +1311,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B11" s="4">
         <f>$B$8</f>
@@ -1331,7 +1328,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B12" s="4">
         <f>B11*(1+$B$6)</f>
@@ -1348,7 +1345,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="B13" s="4">
         <f>B12*(1+$B$6)</f>
@@ -1365,7 +1362,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="B14" s="4">
         <f>B13*(1+$B$6)</f>
@@ -1382,7 +1379,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="B15" s="4">
         <f>B14*(1+$B$6)</f>
@@ -1399,7 +1396,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="B16" s="4">
         <f>B15*(1+$B$6)</f>
@@ -1422,7 +1419,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>≈ 2027–28</t>
+          <t>≈ 2028–29</t>
         </is>
       </c>
     </row>
@@ -1861,7 +1858,7 @@
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>8939036</v>
+        <v>8370000</v>
       </c>
       <c r="E14" t="n">
         <v>800</v>
@@ -1899,7 +1896,7 @@
         </is>
       </c>
       <c r="D15" s="4" t="n">
-        <v>8370000</v>
+        <v>7961500</v>
       </c>
       <c r="E15" t="n">
         <v>738</v>
